--- a/tests/realSuite/Piano-Viaggi_Atletica-IS_7-maggio-2025_def_con-cell-5/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Atletica-IS_7-maggio-2025_def_con-cell-5/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,37 +436,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IS Degasperi Borgo Valsugana</t>
+          <t>IS Buonarroti Trento</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stazione autocorriere, Borgo Valsugana</t>
+          <t>Fermata Bus Funivia Sardagna - Trento</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IS Floriani Riva del Garda</t>
+          <t>IS Degasperi Borgo Valsugana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scuola – Viale dei Tigli, Riva del Garda</t>
+          <t>Stazione autocorriere, Borgo Valsugana</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IS Guetti Tione</t>
+          <t>IS Enaip Tione</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,141 +475,171 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IS Maffei Riva del Garda</t>
+          <t>IS Floriani Riva del Garda</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fermata bus – Viale Martiri, Riva del Garda</t>
+          <t>Scuola – Viale dei Tigli, Riva del Garda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IS Martini Mezzolombardo</t>
+          <t>IS Guetti Tione</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scuola – Via Perlasca, Mezzolombardo</t>
+          <t>Scuola – Via Durone, Tione</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IS Pertini Trento</t>
+          <t>IS Maffei Riva del Garda</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Funivia Sardagna - Trento</t>
+          <t>Fermata bus – Viale Martiri, Riva del Garda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IS Pilati CLES</t>
+          <t>IS Martini Mezzolombardo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Piazza Fiera, Cles</t>
+          <t>Scuola – Via Perlasca, Mezzolombardo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IS Rosmini Trento</t>
+          <t>IS Pertini Trento</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Corso 3 Novembre – Fermata Autobus (Cavalleggeri) - Trento</t>
+          <t>Funivia Sardagna - Trento</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IS Russell CLES</t>
+          <t>IS Pilati CLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cles (stessa area di raccolta bus)</t>
+          <t>Piazza Fiera, Cles</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liceo Da Vinci Trento</t>
+          <t>IS Rosmini Trento</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fermata Bus Cimitero - direzione sud - Via Giusti - Trento</t>
+          <t>Corso 3 Novembre – Fermata Autobus (Cavalleggeri) - Trento</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Liceo Da Vinci Trento (pullman con pedana)</t>
+          <t>IS Russell CLES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fermata Bus Cimitero - direzione sud - Via Giusti - Trento</t>
+          <t>Cles (stessa area di raccolta bus)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Liceo Da Vinci Trento</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fermata Bus Cimitero - direzione sud - Via Giusti - Trento</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Liceo Da Vinci Trento (pullman con pedana)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fermata Bus Cimitero - direzione sud - Via Giusti - Trento</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Linguistico SCHOLL Trento</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Fermata Bus Funivia Sardagna - Trento</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C15" t="n">
         <v>27</v>
       </c>
     </row>
